--- a/academias/Inglés - Estadisticos 20241.xlsx
+++ b/academias/Inglés - Estadisticos 20241.xlsx
@@ -1087,19 +1087,19 @@
         <v>41</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>82.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>17.1</v>
+        <v>14.6</v>
       </c>
       <c r="I16" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1224,16 +1224,16 @@
         <v>168</v>
       </c>
       <c r="E20">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F20">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" s="1">
-        <v>80.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="H20" s="1">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="I20" s="2">
         <v>7.8</v>
@@ -1259,19 +1259,19 @@
         <v>33</v>
       </c>
       <c r="E21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21" s="1">
-        <v>66.7</v>
+        <v>69.7</v>
       </c>
       <c r="H21" s="1">
-        <v>33.3</v>
+        <v>30.3</v>
       </c>
       <c r="I21" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1466,16 +1466,16 @@
         <v>195</v>
       </c>
       <c r="E27">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" s="1">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="H27" s="1">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="I27" s="2">
         <v>8.699999999999999</v>
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>5.9</v>
       </c>
       <c r="I33" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1944,16 +1944,16 @@
         <v>987</v>
       </c>
       <c r="E41">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="F41">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G41" s="1">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="H41" s="1">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="I41" s="2">
         <v>7.5</v>
@@ -2030,25 +2030,25 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2065,25 +2065,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2100,25 +2100,25 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2135,25 +2135,25 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>5.7</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2170,25 +2170,25 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>95.8</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2205,25 +2205,25 @@
         <v>37</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2237,25 +2237,25 @@
         <v>184</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="F8">
-        <v>184</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>96.2</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>3.8</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J8">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2272,25 +2272,25 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>38.1</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J9">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2307,25 +2307,25 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2342,25 +2342,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2377,25 +2377,25 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>27.8</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2412,25 +2412,25 @@
         <v>23</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>17.4</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2444,25 +2444,25 @@
         <v>108</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F14">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>19.4</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2479,25 +2479,25 @@
         <v>40</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2514,25 +2514,25 @@
         <v>41</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>17.1</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2549,25 +2549,25 @@
         <v>28</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>3.6</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J17">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2584,25 +2584,25 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>6.5</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J18">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2619,25 +2619,25 @@
         <v>28</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F19">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2651,25 +2651,25 @@
         <v>168</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="F20">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2686,25 +2686,25 @@
         <v>33</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F21">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>78.8</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>21.2</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J21">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2721,25 +2721,25 @@
         <v>41</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F22">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2756,25 +2756,25 @@
         <v>40</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F23">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J23">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2791,25 +2791,25 @@
         <v>36</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J24">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2826,25 +2826,25 @@
         <v>20</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J25">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2861,25 +2861,25 @@
         <v>25</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F26">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J26">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2893,25 +2893,25 @@
         <v>195</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="F27">
-        <v>195</v>
+        <v>9</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>4.6</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -3033,25 +3033,25 @@
         <v>33</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F31">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
       <c r="I31" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J31">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3100,25 +3100,25 @@
         <v>188</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F33">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="I33" s="2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J33">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3135,25 +3135,25 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>35.9</v>
       </c>
       <c r="I34" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J34">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3170,25 +3170,25 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F35">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>64.7</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J35">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3342,25 +3342,25 @@
         <v>144</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F40">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>25.7</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>74.3</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J40">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3371,25 +3371,25 @@
         <v>987</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="F41">
-        <v>987</v>
+        <v>326</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H41" s="1">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="I41" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J41">
-        <v>987</v>
+        <v>226</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>22.9</v>
       </c>
     </row>
   </sheetData>
@@ -3457,19 +3457,19 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>91.7</v>
+        <v>87.5</v>
       </c>
       <c r="H2" s="1">
-        <v>8.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I2" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3504,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3539,7 +3539,7 @@
         <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3562,19 +3562,19 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="H5" s="1">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H6" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I6" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3632,19 +3632,19 @@
         <v>37</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3664,19 +3664,19 @@
         <v>184</v>
       </c>
       <c r="E8">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>94.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="H8" s="1">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3699,19 +3699,19 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>57.1</v>
+        <v>61.9</v>
       </c>
       <c r="H9" s="1">
-        <v>42.9</v>
+        <v>38.1</v>
       </c>
       <c r="I9" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3734,19 +3734,19 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H10" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3781,7 +3781,7 @@
         <v>4.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3804,19 +3804,19 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>66.7</v>
+        <v>72.2</v>
       </c>
       <c r="H12" s="1">
-        <v>33.3</v>
+        <v>27.8</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3839,19 +3839,19 @@
         <v>23</v>
       </c>
       <c r="E13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>73.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>26.1</v>
+        <v>17.4</v>
       </c>
       <c r="I13" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3871,19 +3871,19 @@
         <v>108</v>
       </c>
       <c r="E14">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G14" s="1">
-        <v>75</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>25</v>
+        <v>19.4</v>
       </c>
       <c r="I14" s="2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3906,19 +3906,19 @@
         <v>40</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="H15" s="1">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="I15" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         <v>17.1</v>
       </c>
       <c r="I16" s="2">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3976,19 +3976,19 @@
         <v>28</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>89.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="I17" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4011,19 +4011,19 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>77.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="H18" s="1">
-        <v>22.6</v>
+        <v>6.5</v>
       </c>
       <c r="I18" s="2">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4046,19 +4046,19 @@
         <v>28</v>
       </c>
       <c r="E19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>82.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H19" s="1">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="I19" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4078,19 +4078,19 @@
         <v>168</v>
       </c>
       <c r="E20">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F20">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G20" s="1">
-        <v>80.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="H20" s="1">
-        <v>19.6</v>
+        <v>14.3</v>
       </c>
       <c r="I20" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4113,19 +4113,19 @@
         <v>33</v>
       </c>
       <c r="E21">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1">
-        <v>66.7</v>
+        <v>78.8</v>
       </c>
       <c r="H21" s="1">
-        <v>33.3</v>
+        <v>21.2</v>
       </c>
       <c r="I21" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         <v>2.4</v>
       </c>
       <c r="I22" s="2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>195</v>
       </c>
       <c r="E27">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G27" s="1">
-        <v>93.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="I27" s="2">
         <v>8.699999999999999</v>
@@ -4367,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4460,19 +4460,19 @@
         <v>33</v>
       </c>
       <c r="E31">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I31" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4527,19 +4527,19 @@
         <v>188</v>
       </c>
       <c r="E33">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F33">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G33" s="1">
-        <v>94.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="I33" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4562,19 +4562,19 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>28.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>71.8</v>
+        <v>35.9</v>
       </c>
       <c r="I34" s="2">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4597,19 +4597,19 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F35">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G35" s="1">
-        <v>32.4</v>
+        <v>35.3</v>
       </c>
       <c r="H35" s="1">
-        <v>67.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="I35" s="2">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4769,19 +4769,19 @@
         <v>144</v>
       </c>
       <c r="E40">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F40">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G40" s="1">
-        <v>41.7</v>
+        <v>52.1</v>
       </c>
       <c r="H40" s="1">
-        <v>58.3</v>
+        <v>47.9</v>
       </c>
       <c r="I40" s="2">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4798,19 +4798,19 @@
         <v>987</v>
       </c>
       <c r="E41">
-        <v>809</v>
+        <v>843</v>
       </c>
       <c r="F41">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="G41" s="1">
-        <v>82</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H41" s="1">
-        <v>18</v>
+        <v>14.6</v>
       </c>
       <c r="I41" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J41">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20241.xlsx
+++ b/academias/Inglés - Estadisticos 20241.xlsx
@@ -2928,25 +2928,25 @@
         <v>48</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F28">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J28">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2963,25 +2963,25 @@
         <v>36</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F29">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2998,25 +2998,25 @@
         <v>37</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F30">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>83.8</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>16.2</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J30">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3068,25 +3068,25 @@
         <v>34</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F32">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>20.6</v>
       </c>
       <c r="I32" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J32">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3100,25 +3100,25 @@
         <v>188</v>
       </c>
       <c r="E33">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="F33">
-        <v>158</v>
+        <v>27</v>
       </c>
       <c r="G33" s="1">
-        <v>16</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>84</v>
+        <v>14.4</v>
       </c>
       <c r="I33" s="2">
-        <v>1.7</v>
+        <v>7.9</v>
       </c>
       <c r="J33">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>82.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3205,25 +3205,25 @@
         <v>23</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>56.5</v>
       </c>
       <c r="I36" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J36">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3240,25 +3240,25 @@
         <v>19</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F37">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J37">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3275,25 +3275,25 @@
         <v>19</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F38">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>36.8</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J38">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3310,25 +3310,25 @@
         <v>10</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I39" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J39">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3342,25 +3342,25 @@
         <v>144</v>
       </c>
       <c r="E40">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="F40">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="G40" s="1">
-        <v>25.7</v>
+        <v>56.9</v>
       </c>
       <c r="H40" s="1">
-        <v>74.3</v>
+        <v>43.1</v>
       </c>
       <c r="I40" s="2">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="J40">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>49.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -3371,25 +3371,25 @@
         <v>987</v>
       </c>
       <c r="E41">
-        <v>661</v>
+        <v>837</v>
       </c>
       <c r="F41">
-        <v>326</v>
+        <v>150</v>
       </c>
       <c r="G41" s="1">
-        <v>67</v>
+        <v>84.8</v>
       </c>
       <c r="H41" s="1">
-        <v>33</v>
+        <v>15.2</v>
       </c>
       <c r="I41" s="2">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="J41">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>22.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4355,19 +4355,19 @@
         <v>48</v>
       </c>
       <c r="E28">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I28" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4390,19 +4390,19 @@
         <v>36</v>
       </c>
       <c r="E29">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I29" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4425,19 +4425,19 @@
         <v>37</v>
       </c>
       <c r="E30">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G30" s="1">
-        <v>100</v>
+        <v>83.8</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="I30" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4495,19 +4495,19 @@
         <v>34</v>
       </c>
       <c r="E32">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F32">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G32" s="1">
-        <v>67.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H32" s="1">
-        <v>32.4</v>
+        <v>20.6</v>
       </c>
       <c r="I32" s="2">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4527,19 +4527,19 @@
         <v>188</v>
       </c>
       <c r="E33">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="F33">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G33" s="1">
-        <v>92.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>7.4</v>
+        <v>14.4</v>
       </c>
       <c r="I33" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4632,19 +4632,19 @@
         <v>23</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G36" s="1">
-        <v>34.8</v>
+        <v>43.5</v>
       </c>
       <c r="H36" s="1">
-        <v>65.2</v>
+        <v>56.5</v>
       </c>
       <c r="I36" s="2">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4667,19 +4667,19 @@
         <v>19</v>
       </c>
       <c r="E37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G37" s="1">
-        <v>63.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H37" s="1">
-        <v>36.8</v>
+        <v>21.1</v>
       </c>
       <c r="I37" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4714,7 +4714,7 @@
         <v>36.8</v>
       </c>
       <c r="I38" s="2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4737,19 +4737,19 @@
         <v>10</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G39" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H39" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I39" s="2">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4769,19 +4769,19 @@
         <v>144</v>
       </c>
       <c r="E40">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F40">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G40" s="1">
-        <v>52.1</v>
+        <v>56.9</v>
       </c>
       <c r="H40" s="1">
-        <v>47.9</v>
+        <v>43.1</v>
       </c>
       <c r="I40" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4798,19 +4798,19 @@
         <v>987</v>
       </c>
       <c r="E41">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="F41">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="G41" s="1">
-        <v>85.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="H41" s="1">
-        <v>14.6</v>
+        <v>15.2</v>
       </c>
       <c r="I41" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J41">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20241.xlsx
+++ b/academias/Inglés - Estadisticos 20241.xlsx
@@ -982,22 +982,22 @@
         <v>32</v>
       </c>
       <c r="D13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13">
         <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>73.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="H13" s="1">
-        <v>26.1</v>
+        <v>25</v>
       </c>
       <c r="I13" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1014,19 +1014,19 @@
         <v>18</v>
       </c>
       <c r="D14">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14">
         <v>27</v>
       </c>
       <c r="G14" s="1">
-        <v>75</v>
+        <v>75.2</v>
       </c>
       <c r="H14" s="1">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="I14" s="2">
         <v>7</v>
@@ -1119,22 +1119,22 @@
         <v>35</v>
       </c>
       <c r="D17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17" s="1">
-        <v>89.3</v>
+        <v>89.7</v>
       </c>
       <c r="H17" s="1">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="I17" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1221,19 +1221,19 @@
         <v>18</v>
       </c>
       <c r="D20">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E20">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F20">
         <v>32</v>
       </c>
       <c r="G20" s="1">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="I20" s="2">
         <v>7.8</v>
@@ -1326,10 +1326,10 @@
         <v>40</v>
       </c>
       <c r="D23">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E23">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>42</v>
       </c>
       <c r="D25">
+        <v>21</v>
+      </c>
+      <c r="E25">
         <v>20</v>
-      </c>
-      <c r="E25">
-        <v>19</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="H25" s="1">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I25" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1431,10 +1431,10 @@
         <v>43</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1463,22 +1463,22 @@
         <v>18</v>
       </c>
       <c r="D27">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E27">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F27">
         <v>12</v>
       </c>
       <c r="G27" s="1">
-        <v>93.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I27" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1941,22 +1941,22 @@
         <v>21</v>
       </c>
       <c r="D41">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="E41">
-        <v>811</v>
+        <v>822</v>
       </c>
       <c r="F41">
         <v>176</v>
       </c>
       <c r="G41" s="1">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H41" s="1">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="I41" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>4.2</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>3.8</v>
       </c>
       <c r="I8" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2409,19 +2409,19 @@
         <v>32</v>
       </c>
       <c r="D13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H13" s="1">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="I13" s="2">
         <v>7.6</v>
@@ -2441,19 +2441,19 @@
         <v>18</v>
       </c>
       <c r="D14">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>21</v>
       </c>
       <c r="G14" s="1">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="H14" s="1">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="I14" s="2">
         <v>7.4</v>
@@ -2546,22 +2546,22 @@
         <v>35</v>
       </c>
       <c r="D17">
+        <v>29</v>
+      </c>
+      <c r="E17">
         <v>28</v>
-      </c>
-      <c r="E17">
-        <v>27</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I17" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2648,19 +2648,19 @@
         <v>18</v>
       </c>
       <c r="D20">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E20">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F20">
         <v>24</v>
       </c>
       <c r="G20" s="1">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="H20" s="1">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="I20" s="2">
         <v>8</v>
@@ -2753,10 +2753,10 @@
         <v>40</v>
       </c>
       <c r="D23">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E23">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2823,22 +2823,22 @@
         <v>42</v>
       </c>
       <c r="D25">
+        <v>21</v>
+      </c>
+      <c r="E25">
         <v>20</v>
-      </c>
-      <c r="E25">
-        <v>19</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="H25" s="1">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I25" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -2858,10 +2858,10 @@
         <v>43</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -2890,22 +2890,22 @@
         <v>18</v>
       </c>
       <c r="D27">
+        <v>204</v>
+      </c>
+      <c r="E27">
         <v>195</v>
-      </c>
-      <c r="E27">
-        <v>186</v>
       </c>
       <c r="F27">
         <v>9</v>
       </c>
       <c r="G27" s="1">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I27" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3368,19 +3368,19 @@
         <v>21</v>
       </c>
       <c r="D41">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="E41">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="F41">
         <v>150</v>
       </c>
       <c r="G41" s="1">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="H41" s="1">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="I41" s="2">
         <v>8</v>
@@ -3457,16 +3457,16 @@
         <v>24</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="H2" s="1">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2" s="2">
         <v>8.1</v>
@@ -3504,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3539,7 +3539,7 @@
         <v>3.6</v>
       </c>
       <c r="I4" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3562,19 +3562,19 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3632,19 +3632,19 @@
         <v>37</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I7" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3664,16 +3664,16 @@
         <v>184</v>
       </c>
       <c r="E8">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>96.2</v>
+        <v>97.8</v>
       </c>
       <c r="H8" s="1">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="I8" s="2">
         <v>8.6</v>
@@ -3836,19 +3836,19 @@
         <v>32</v>
       </c>
       <c r="D13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H13" s="1">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="I13" s="2">
         <v>7.5</v>
@@ -3868,19 +3868,19 @@
         <v>18</v>
       </c>
       <c r="D14">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>21</v>
       </c>
       <c r="G14" s="1">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="H14" s="1">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="I14" s="2">
         <v>7.3</v>
@@ -3973,22 +3973,22 @@
         <v>35</v>
       </c>
       <c r="D17">
+        <v>29</v>
+      </c>
+      <c r="E17">
         <v>28</v>
-      </c>
-      <c r="E17">
-        <v>27</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="I17" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4075,19 +4075,19 @@
         <v>18</v>
       </c>
       <c r="D20">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E20">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F20">
         <v>24</v>
       </c>
       <c r="G20" s="1">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="H20" s="1">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="I20" s="2">
         <v>8</v>
@@ -4180,10 +4180,10 @@
         <v>40</v>
       </c>
       <c r="D23">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E23">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -4195,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4250,19 +4250,19 @@
         <v>42</v>
       </c>
       <c r="D25">
+        <v>21</v>
+      </c>
+      <c r="E25">
         <v>20</v>
-      </c>
-      <c r="E25">
-        <v>19</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="H25" s="1">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I25" s="2">
         <v>8.300000000000001</v>
@@ -4285,10 +4285,10 @@
         <v>43</v>
       </c>
       <c r="D26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4317,19 +4317,19 @@
         <v>18</v>
       </c>
       <c r="D27">
+        <v>204</v>
+      </c>
+      <c r="E27">
         <v>195</v>
-      </c>
-      <c r="E27">
-        <v>186</v>
       </c>
       <c r="F27">
         <v>9</v>
       </c>
       <c r="G27" s="1">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I27" s="2">
         <v>8.699999999999999</v>
@@ -4562,19 +4562,19 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F34">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G34" s="1">
-        <v>64.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="H34" s="1">
-        <v>35.9</v>
+        <v>7.7</v>
       </c>
       <c r="I34" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -4597,19 +4597,19 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F35">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1">
-        <v>35.3</v>
+        <v>91.2</v>
       </c>
       <c r="H35" s="1">
-        <v>64.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I35" s="2">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4632,19 +4632,19 @@
         <v>23</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F36">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>43.5</v>
+        <v>100</v>
       </c>
       <c r="H36" s="1">
-        <v>56.5</v>
+        <v>0</v>
       </c>
       <c r="I36" s="2">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -4667,19 +4667,19 @@
         <v>19</v>
       </c>
       <c r="E37">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G37" s="1">
-        <v>78.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="H37" s="1">
-        <v>21.1</v>
+        <v>5.3</v>
       </c>
       <c r="I37" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4702,16 +4702,16 @@
         <v>19</v>
       </c>
       <c r="E38">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1">
-        <v>63.2</v>
+        <v>94.7</v>
       </c>
       <c r="H38" s="1">
-        <v>36.8</v>
+        <v>5.3</v>
       </c>
       <c r="I38" s="2">
         <v>7.2</v>
@@ -4737,19 +4737,19 @@
         <v>10</v>
       </c>
       <c r="E39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H39" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4769,19 +4769,19 @@
         <v>144</v>
       </c>
       <c r="E40">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="F40">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="G40" s="1">
-        <v>56.9</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H40" s="1">
-        <v>43.1</v>
+        <v>5.6</v>
       </c>
       <c r="I40" s="2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4795,22 +4795,22 @@
         <v>21</v>
       </c>
       <c r="D41">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="E41">
-        <v>837</v>
+        <v>905</v>
       </c>
       <c r="F41">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="G41" s="1">
-        <v>84.8</v>
+        <v>90.7</v>
       </c>
       <c r="H41" s="1">
-        <v>15.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I41" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J41">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20241.xlsx
+++ b/academias/Inglés - Estadisticos 20241.xlsx
@@ -3699,19 +3699,19 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>61.9</v>
+        <v>85.7</v>
       </c>
       <c r="H9" s="1">
-        <v>38.1</v>
+        <v>14.3</v>
       </c>
       <c r="I9" s="2">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3734,19 +3734,19 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H10" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I10" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3781,7 +3781,7 @@
         <v>4.8</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3871,19 +3871,19 @@
         <v>109</v>
       </c>
       <c r="E14">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G14" s="1">
-        <v>80.7</v>
+        <v>87.2</v>
       </c>
       <c r="H14" s="1">
-        <v>19.3</v>
+        <v>12.8</v>
       </c>
       <c r="I14" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4798,16 +4798,16 @@
         <v>998</v>
       </c>
       <c r="E41">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="F41">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G41" s="1">
-        <v>90.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H41" s="1">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I41" s="2">
         <v>8</v>

--- a/academias/Inglés - Estadisticos 20241.xlsx
+++ b/academias/Inglés - Estadisticos 20241.xlsx
@@ -3804,19 +3804,19 @@
         <v>18</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3839,19 +3839,19 @@
         <v>24</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3871,19 +3871,19 @@
         <v>109</v>
       </c>
       <c r="E14">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>87.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>12.8</v>
+        <v>4.6</v>
       </c>
       <c r="I14" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3906,19 +3906,19 @@
         <v>40</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>75</v>
+        <v>92.5</v>
       </c>
       <c r="H15" s="1">
-        <v>25</v>
+        <v>7.5</v>
       </c>
       <c r="I15" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3941,16 +3941,16 @@
         <v>41</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>82.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="H16" s="1">
-        <v>17.1</v>
+        <v>7.3</v>
       </c>
       <c r="I16" s="2">
         <v>7.6</v>
@@ -3976,19 +3976,19 @@
         <v>29</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4011,19 +4011,19 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4046,19 +4046,19 @@
         <v>28</v>
       </c>
       <c r="E19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="H19" s="1">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="I19" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4078,19 +4078,19 @@
         <v>169</v>
       </c>
       <c r="E20">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="F20">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>85.8</v>
+        <v>94.7</v>
       </c>
       <c r="H20" s="1">
-        <v>14.2</v>
+        <v>5.3</v>
       </c>
       <c r="I20" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>21.2</v>
       </c>
       <c r="I21" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4148,19 +4148,19 @@
         <v>41</v>
       </c>
       <c r="E22">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4183,19 +4183,19 @@
         <v>44</v>
       </c>
       <c r="E23">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I23" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4253,19 +4253,19 @@
         <v>21</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4320,19 +4320,19 @@
         <v>204</v>
       </c>
       <c r="E27">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="1">
-        <v>95.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H27" s="1">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I27" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4355,19 +4355,19 @@
         <v>48</v>
       </c>
       <c r="E28">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F28">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G28" s="1">
-        <v>83.3</v>
+        <v>95.8</v>
       </c>
       <c r="H28" s="1">
-        <v>16.7</v>
+        <v>4.2</v>
       </c>
       <c r="I28" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4390,19 +4390,19 @@
         <v>36</v>
       </c>
       <c r="E29">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>91.7</v>
+        <v>97.2</v>
       </c>
       <c r="H29" s="1">
-        <v>8.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I29" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4425,19 +4425,19 @@
         <v>37</v>
       </c>
       <c r="E30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>83.8</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -4460,19 +4460,19 @@
         <v>33</v>
       </c>
       <c r="E31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="1">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="I31" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4495,16 +4495,16 @@
         <v>34</v>
       </c>
       <c r="E32">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G32" s="1">
-        <v>79.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H32" s="1">
-        <v>20.6</v>
+        <v>2.9</v>
       </c>
       <c r="I32" s="2">
         <v>7.1</v>
@@ -4527,19 +4527,19 @@
         <v>188</v>
       </c>
       <c r="E33">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="F33">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G33" s="1">
-        <v>85.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="H33" s="1">
-        <v>14.4</v>
+        <v>3.2</v>
       </c>
       <c r="I33" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4798,16 +4798,16 @@
         <v>998</v>
       </c>
       <c r="E41">
-        <v>912</v>
+        <v>958</v>
       </c>
       <c r="F41">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="G41" s="1">
-        <v>91.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="H41" s="1">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="I41" s="2">
         <v>8</v>
